--- a/Маршруты НБХЗ.xlsx
+++ b/Маршруты НБХЗ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\shop-orders\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{550778FA-4CD8-4FC4-A0E6-783EBE92745B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E45E9DFB-9D26-40F8-B5CD-10F9297CF39A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D340DCD7-CEE9-43E4-AB1E-BB5803681028}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="76">
   <si>
     <t>Амосова 5А</t>
   </si>
@@ -953,19 +953,22 @@
         <v>32</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H32" s="2"/>
     </row>
-    <row r="33" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D33" s="4" t="s">
         <v>33</v>
       </c>
       <c r="E33" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H33" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D34" s="4" t="s">
         <v>34</v>
       </c>
@@ -973,7 +976,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D35" s="4" t="s">
         <v>8</v>
       </c>
@@ -981,7 +984,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D36" s="4" t="s">
         <v>9</v>
       </c>
@@ -989,7 +992,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D37" s="4" t="s">
         <v>35</v>
       </c>
@@ -997,7 +1000,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D38" s="4" t="s">
         <v>36</v>
       </c>
